--- a/templates/excel/Trade_Based_Estimate_Workbook.xlsx
+++ b/templates/excel/Trade_Based_Estimate_Workbook.xlsx
@@ -2605,7 +2605,7 @@
     <row r="26" ht="15" customHeight="1" s="37">
       <c r="A26" s="71" t="inlineStr">
         <is>
-          <t>2. Payment terms: As per contract or 50% deposit, balance on completion.</t>
+          <t>2. Payment terms: as per the contract. Any deposit will not exceed the legal limit for building work in your state.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
     <row r="29" ht="15" customHeight="1" s="37">
       <c r="A29" s="71" t="inlineStr">
         <is>
-          <t>5. Work carried out per Australian Standards and BCA requirements.</t>
+          <t>5. Work carried out to the National Construction Code (NCC) and relevant Australian Standards.</t>
         </is>
       </c>
     </row>
@@ -2654,9 +2654,9 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A7:E7"/>
